--- a/EMS_QR_Codes.xlsx
+++ b/EMS_QR_Codes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\เอกสาร\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\EMS Stock Managment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F0F903-D2FF-42CA-93FD-9612D52A17F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792BF24E-DA3D-406E-B5F6-EEACFF855987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
   <si>
     <t>รหัส</t>
   </si>
@@ -629,6 +629,12 @@
   </si>
   <si>
     <t>กรรไกรตัดพลาสเตอร์ 22 cm.</t>
+  </si>
+  <si>
+    <t>จำนวนสต๊อก(ไม่ต่ำกว่า)</t>
+  </si>
+  <si>
+    <t>จำนวนที่มีอยู่</t>
   </si>
 </sst>
 </file>
@@ -4382,16 +4388,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="27" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="11"/>
     <col min="2" max="2" width="55.6640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.109375" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="2"/>
+    <col min="4" max="4" width="25.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -4401,8 +4409,14 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="D1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
@@ -4410,7 +4424,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
@@ -4418,7 +4432,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A4" s="11" t="s">
         <v>4</v>
       </c>
@@ -4426,7 +4440,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A5" s="11" t="s">
         <v>5</v>
       </c>
@@ -4434,7 +4448,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A6" s="11" t="s">
         <v>6</v>
       </c>
@@ -4442,7 +4456,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A7" s="11" t="s">
         <v>7</v>
       </c>
@@ -4450,7 +4464,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A8" s="11" t="s">
         <v>8</v>
       </c>
@@ -4458,7 +4472,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A9" s="11" t="s">
         <v>9</v>
       </c>
@@ -4466,7 +4480,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
@@ -4474,7 +4488,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
@@ -4482,7 +4496,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A12" s="11" t="s">
         <v>12</v>
       </c>
@@ -4490,7 +4504,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A13" s="11" t="s">
         <v>13</v>
       </c>
@@ -4498,7 +4512,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A14" s="11" t="s">
         <v>14</v>
       </c>
@@ -4506,7 +4520,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
@@ -4514,7 +4528,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:5" ht="64.95" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
